--- a/site/Entra-ID-Dayforce-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Dayforce-Writeback-Integration-Guide/headings.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D19"/>
+  <dimension ref="A1:D33"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -617,95 +617,95 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Policy</t>
+          <t>Directory Configuration</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KSEWDF1JFQ62X6MYHDNS21YD</t>
+          <t>h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDF1JFQ62X6MYHDNS21YD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Execution</t>
+          <t>Data Synchronization Settings</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Conditional WriteBack</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>h_01KSF8NGEC1PVW267CXYD565VC</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGEC1PVW267CXYD565VC</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Entra application</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KSF8NGECQ0F451G6V9SAN23V</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGECQ0F451G6V9SAN23V</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>WriteBack Settings</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -715,63 +715,63 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KSF8KZ7D37FNE7ETRKTHYZKE</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8KZ7D37FNE7ETRKTHYZKE</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Match Employees Between Entra ID &amp; Dayforce</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KSF8NMQWYEKR2WHV9HP5A8BG</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NMQWYEKR2WHV9HP5A8BG</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>WriteBack Settings</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KSF8NMQWQW26YFD6YYX66GKM</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NMQWQW26YFD6YYX66GKM</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Schedule</t>
+          <t>Policy</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -781,54 +781,362 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>h_01KSEWDF1JFQ62X6MYHDNS21YD</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDF1JFQ62X6MYHDNS21YD</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Execute Integration</t>
+          <t>PII Attribute</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>H1</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>h_01KSF8DCBJTH8PNYQ6NJR35QEV</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8DCBJTH8PNYQ6NJR35QEV</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
+          <t>Execution</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDR3371Y9MTXCR3HYP7NV</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Advance Settings</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1W5D3KG4Q8Z44BMB8CBYQ5</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>RollOut Configurations</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEYSMD2TT1HVSSCGWM0SWYA</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>Debug Filter - Writeback</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>h_01KSEZ1N41WY3X8THTWYC1NQ3Q</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEZ1N41WY3X8THTWYC1NQ3Q</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Operational Settings</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN47NYDZ014D07BNJKKQFDED</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Global Operational Settings</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>h_01KSF5372WEE5N0116GPM4DMFK</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF5372WEE5N0116GPM4DMFK</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Operational Settings Definition</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>H4</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>h_01KSF5FFVWP7PPYSWJRZ2EJD44</t>
+        </is>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF5FFVWP7PPYSWJRZ2EJD44</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Notification</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+        </is>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Channels</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Template Library</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Configuration</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>H3</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Tables</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Schedule</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>H2</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KJCP43MS8PMZZMVQPMDWVEEP</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Execute Integration</t>
+        </is>
+      </c>
+      <c r="B32" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C32" t="inlineStr">
+        <is>
+          <t>h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01J6YAY9KXHRE6D4TDZNBCBHEF</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
           <t>Additional Options</t>
         </is>
       </c>
-      <c r="B19" t="inlineStr">
+      <c r="B33" t="inlineStr">
         <is>
           <t>H1</t>
         </is>
       </c>
-      <c r="C19" t="inlineStr">
+      <c r="C33" t="inlineStr">
         <is>
           <t>h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>
       </c>
-      <c r="D19" t="inlineStr">
+      <c r="D33" t="inlineStr">
         <is>
           <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01K06FZJ20WACCTKEZJPE2D9JK</t>
         </is>

--- a/site/Entra-ID-Dayforce-Writeback-Integration-Guide/headings.xlsx
+++ b/site/Entra-ID-Dayforce-Writeback-Integration-Guide/headings.xlsx
@@ -595,73 +595,73 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Directory</t>
+          <t>Select Source Application</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>h_01KSEWD7Y1Y8545Z9Y4CFFHB1E</t>
+          <t>h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWD7Y1Y8545Z9Y4CFFHB1E</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSHSPK4YPRBW9YH5JQX4JXN3</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Directory Configuration</t>
+          <t>Directory</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
+          <t>h_01KSEWD7Y1Y8545Z9Y4CFFHB1E</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWD7Y1Y8545Z9Y4CFFHB1E</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Synchronization Settings</t>
+          <t>Directory Configuration</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>H4</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>h_01KSF8NGECRJN5RPS871WR2368</t>
+          <t>h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGECRJN5RPS871WR2368</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8KZ7BRYCY5BZGXXXVMTM2</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Conditional WriteBack</t>
+          <t>Data Synchronization Settings</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -671,12 +671,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>h_01KSF8NGEC1PVW267CXYD565VC</t>
+          <t>h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGEC1PVW267CXYD565VC</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF8NGECRJN5RPS871WR2368</t>
         </is>
       </c>
     </row>
@@ -925,7 +925,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Global Operational Settings</t>
+          <t>Logging Settings</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -935,19 +935,19 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>h_01KSF5372WEE5N0116GPM4DMFK</t>
+          <t>h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF5372WEE5N0116GPM4DMFK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSHXF7YZXW8XYHPBW0GGX85G</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Operational Settings Definition</t>
+          <t>Report Settings</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -957,63 +957,63 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>h_01KSF5FFVWP7PPYSWJRZ2EJD44</t>
+          <t>h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSF5FFVWP7PPYSWJRZ2EJD44</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSHXF7Z06V0RVBS9CW6CEYFP</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Notification</t>
+          <t>Log Insights Settings</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H4</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>h_01KSHXF7Z0MW8W49X4TTD453F9</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSHXF7Z0MW8W49X4TTD453F9</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Channels</t>
+          <t>Notification</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>H3</t>
+          <t>H2</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KSEWDZWGHZ8G8RDA1E958XZK</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Template Library</t>
+          <t>Channels</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
@@ -1023,19 +1023,19 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVC1MJHX5RB3ETN8MHCM7</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Configuration</t>
+          <t>Template Library</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1045,34 +1045,34 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVFK47V9644J22EQEDVZE</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Tables</t>
+          <t>Configuration</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>H2</t>
+          <t>H3</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KMQ7WN0WEE2127MZ5RDTFBWD</t>
+          <t>https://nawabahmadreshi.github.io/zendesk-helpcenter-sit/Entra-ID-Dayforce-Writeback-Integration-Guide/#h_01KN1AVMW81679JNM3NZGGKJAY</t>
         </is>
       </c>
     </row>
